--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 ELK ANTLERLESS PRIVATE LANDS ONLY.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 ELK ANTLERLESS PRIVATE LANDS ONLY.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hunt Table'!$A$1:$O$28</definedName>
@@ -829,7 +829,11 @@
           <t>53.5</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
           <t>3.7</t>
@@ -890,7 +894,11 @@
           <t>46.7</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
           <t>10.4</t>
@@ -951,7 +959,11 @@
           <t>55.6</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
           <t>11.3</t>
@@ -1012,7 +1024,11 @@
           <t>27.8</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
           <t>7.0</t>
@@ -1073,7 +1089,11 @@
           <t>26.2</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
           <t>15.4</t>
@@ -1134,7 +1154,11 @@
           <t>41.6</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
           <t>9.7</t>
@@ -1195,7 +1219,11 @@
           <t>53.1</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
           <t>5.4</t>
@@ -1256,7 +1284,11 @@
           <t>37.8</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
           <t>6.6</t>
@@ -1317,7 +1349,11 @@
           <t>40.9</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
           <t>3.4</t>
@@ -1378,7 +1414,11 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
           <t>9.8</t>
@@ -1439,7 +1479,11 @@
           <t>36.7</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
           <t>11.4</t>
@@ -1500,7 +1544,11 @@
           <t>60.0</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
           <t>6.0</t>
@@ -1561,7 +1609,11 @@
           <t>48.1</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
           <t>10.1</t>
@@ -1622,7 +1674,11 @@
           <t>30.0</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
           <t>13.7</t>
@@ -1744,7 +1800,11 @@
           <t>21.4</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
           <t>5.8</t>
@@ -1927,7 +1987,11 @@
           <t>42.4</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
           <t>5.5</t>
@@ -1988,7 +2052,11 @@
           <t>34.7</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
           <t>7.2</t>
@@ -2049,7 +2117,11 @@
           <t>53.7</t>
         </is>
       </c>
-      <c r="N25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
           <t>4.8</t>
